--- a/골든래빗 일정.xlsx
+++ b/골든래빗 일정.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Vibe Coding\바로31. 골든레빗 일정\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{390074D3-1397-45A5-AF8E-0857416760A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F70B7BB-4674-4DD0-AD3A-649712182AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3368" windowWidth="14033" windowHeight="12832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="2647" windowWidth="14033" windowHeight="12833" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시트1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="78">
   <si>
     <t>날짜</t>
   </si>
@@ -251,6 +251,10 @@
   </si>
   <si>
     <t>간소화 진행, 17시 업무 마감</t>
+  </si>
+  <si>
+    <t>나</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -260,7 +264,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\.\ m\.\ d"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -279,6 +283,13 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="2">
@@ -301,7 +312,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -318,27 +329,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF535FC1"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF535FC1"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF535FC1"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF535FC1"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -363,13 +361,29 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF535FC1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF535FC1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF535FC1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF535FC1"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="시트1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
-      <tableStyleElement type="headerRow" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -647,8 +661,8 @@
       <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>9</v>
+      <c r="E2" s="6" t="s">
+        <v>77</v>
       </c>
       <c r="F2" s="5" t="b">
         <v>1</v>

--- a/골든래빗 일정.xlsx
+++ b/골든래빗 일정.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Vibe Coding\바로31. 골든레빗 일정\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5E4D937-CDB8-4B3C-8459-4AEC83F74DED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E9751D-18AE-42D8-946D-4D704CCEB133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11183" yWindow="1298" windowWidth="14032" windowHeight="12832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="2647" windowWidth="14033" windowHeight="12833" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시트1" sheetId="1" r:id="rId1"/>
@@ -262,7 +262,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>2분기</t>
+      <t>3분기</t>
     </r>
     <r>
       <rPr>
@@ -374,7 +374,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\.\ m\.\ d"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -742,7 +742,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.265625" customWidth="1"/>
     <col min="2" max="2" width="13.1328125" customWidth="1"/>
@@ -753,7 +753,7 @@
     <col min="7" max="7" width="22.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="22.5" customHeight="1">
+    <row r="1" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -776,7 +776,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="22.5" customHeight="1">
+    <row r="2" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>45992</v>
       </c>
@@ -799,7 +799,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="22.5" customHeight="1">
+    <row r="3" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>45993</v>
       </c>
@@ -822,7 +822,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="22.5" customHeight="1">
+    <row r="4" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>45994</v>
       </c>
@@ -845,7 +845,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="22.5" customHeight="1">
+    <row r="5" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>45995</v>
       </c>
@@ -868,7 +868,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="22.5" customHeight="1">
+    <row r="6" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>45996</v>
       </c>
@@ -891,7 +891,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="22.5" customHeight="1">
+    <row r="7" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>45997</v>
       </c>
@@ -912,7 +912,7 @@
       </c>
       <c r="G7" s="3"/>
     </row>
-    <row r="8" spans="1:7" ht="22.5" customHeight="1">
+    <row r="8" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>45999</v>
       </c>
@@ -935,7 +935,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="22.5" customHeight="1">
+    <row r="9" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>46000</v>
       </c>
@@ -958,7 +958,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="22.5" customHeight="1">
+    <row r="10" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>46001</v>
       </c>
@@ -981,7 +981,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="22.5" customHeight="1">
+    <row r="11" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>46002</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="22.5" customHeight="1">
+    <row r="12" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>46003</v>
       </c>
@@ -1027,7 +1027,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="22.5" customHeight="1">
+    <row r="13" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>46006</v>
       </c>
@@ -1050,7 +1050,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="22.5" customHeight="1">
+    <row r="14" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>46007</v>
       </c>
@@ -1073,7 +1073,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="22.5" customHeight="1">
+    <row r="15" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>46008</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="22.5" customHeight="1">
+    <row r="16" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>46009</v>
       </c>
@@ -1119,7 +1119,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="22.5" customHeight="1">
+    <row r="17" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>46010</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="22.5" customHeight="1">
+    <row r="18" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>46013</v>
       </c>
@@ -1165,7 +1165,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="22.5" customHeight="1">
+    <row r="19" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>46014</v>
       </c>
@@ -1188,7 +1188,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="22.5" customHeight="1">
+    <row r="20" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>46015</v>
       </c>
@@ -1211,7 +1211,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="22.5" customHeight="1">
+    <row r="21" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>46016</v>
       </c>
@@ -1234,7 +1234,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="22.5" customHeight="1">
+    <row r="22" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>46017</v>
       </c>
@@ -1257,7 +1257,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="22.5" customHeight="1">
+    <row r="23" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>46020</v>
       </c>
@@ -1280,7 +1280,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="22.5" customHeight="1">
+    <row r="24" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>46021</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="22.5" customHeight="1">
+    <row r="25" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>46022</v>
       </c>

--- a/골든래빗 일정.xlsx
+++ b/골든래빗 일정.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Vibe Coding\바로31. 골든레빗 일정\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E9751D-18AE-42D8-946D-4D704CCEB133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E17ADC62-4D20-4D0D-9B7A-A90EA77EB502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3675" yWindow="2647" windowWidth="14033" windowHeight="12833" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -262,7 +262,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>3분기</t>
+      <t>3/4분기</t>
     </r>
     <r>
       <rPr>
